--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -824,67 +824,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Skoda 706 RTTN с полуприцепом Alka N12CH   АИСТ</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-2.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-3.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-8.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-9.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-6.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-7.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-5.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-10.jpg</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7409184</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="n">
-        <v>4100</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Škoda</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Автоистория (АИСТ)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>металл , пластик, резина</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Информация по оплате и отправке в разделе " Обо мне". Условия аукциона стандартные. выход на связь в течении 3 дней оплата в течении 7 дней с момента окончания аукциона. Все вопросы по лоту , оплате , отправке исключительно до покупки (до ставки) Смотрите мои другие лоты.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -824,6 +824,67 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Skoda 706 RTTN с полуприцепом Alka N12CH   АИСТ</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-2.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-3.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-8.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-9.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-6.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-7.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-5.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-10.jpg</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7409184</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="n">
+        <v>4100</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Škoda</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>металл , пластик, резина</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>Информация по оплате и отправке в разделе " Обо мне". Условия аукциона стандартные. выход на связь в течении 3 дней оплата в течении 7 дней с момента окончания аукциона. Все вопросы по лоту , оплате , отправке исключительно до покупки (до ставки) Смотрите мои другие лоты.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mercedes Brabus 850 6.0 Widestar  2016 Minichamps</t>
+          <t>Mercedes Brabus G  V12 Widestar 2010  Minichamps</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134535.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134448.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134541.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134547.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20260202_134601.jpg</t>
+          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175143.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175106.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175136.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175148.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175203.jpg</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4213802</t>
+          <t>7151583</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Brabus</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -657,22 +657,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Mercedes Brabus G  V12 Widestar 2010  Minichamps</t>
+          <t>Mercedes C-Klasse 2011 W204 W 204 Schuco</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175143.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175106.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175136.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175148.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175203.jpg</t>
+          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135744.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135654.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135703.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135716.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135721.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135755.jpg</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7151583</t>
+          <t>7830441</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -680,16 +680,16 @@
         <v>300</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9500</v>
+        <v>9300</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Brabus</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>Schuco</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Отправляю по всему миру - по возможности.</t>
+          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкойПривезу любые модели на заказ.</t>
         </is>
       </c>
     </row>
@@ -716,22 +716,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mercedes C-Klasse 2011 W204 W 204 Schuco</t>
+          <t>Audi RS4 RS 4 Avant  2018 Spark</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135744.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135654.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135703.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135716.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135721.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135755.jpg</t>
+          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471219.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471242.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471236.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471229.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471223.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471213.jpg</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7830441</t>
+          <t>9331546</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -739,33 +739,29 @@
         <v>300</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>9300</v>
+        <v>9600</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Audi</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Schuco</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Б/у</t>
+          <t>Новый</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкойПривезу любые модели на заказ.</t>
+          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Привезу любые модели на заказ.</t>
         </is>
       </c>
     </row>
@@ -775,43 +771,49 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Audi RS4 RS 4 Avant  2018 Spark</t>
+          <t>Skoda 706 RTTN с полуприцепом Alka N12CH   АИСТ</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471219.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471242.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471236.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471229.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471223.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471213.jpg</t>
+          <t>https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-2.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-3.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-8.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-9.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-6.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-7.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-5.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-10.jpg</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9331546</t>
+          <t>7409184</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9300</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="n">
-        <v>300</v>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="n">
-        <v>9600</v>
+        <v>4100</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Audi</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Spark</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>металл , пластик, резина</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
@@ -819,67 +821,6 @@
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Привезу любые модели на заказ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Skoda 706 RTTN с полуприцепом Alka N12CH   АИСТ</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-2.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-3.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-8.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-9.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-6.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-7.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-5.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-10.jpg</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7409184</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="n">
-        <v>4100</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Škoda</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Автоистория (АИСТ)</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>металл , пластик, резина</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>Информация по оплате и отправке в разделе " Обо мне". Условия аукциона стандартные. выход на связь в течении 3 дней оплата в течении 7 дней с момента окончания аукциона. Все вопросы по лоту , оплате , отправке исключительно до покупки (до ставки) Смотрите мои другие лоты.</t>
         </is>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -63,13 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -533,299 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Chevrolet Camaro Rally Sport 1978 Neo</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/1734018782485.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1734018782499.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1734018782496.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1734018782493.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1734018782489.jpg</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>4134455</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>9200</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>9500</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Chevrolet</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Neo Scale Models</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Б/у</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Привезу любые модели на заказ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Mercedes Brabus G  V12 Widestar 2010  Minichamps</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175143.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175106.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175136.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175148.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251028_175203.jpg</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>7151583</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>9200</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>9500</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Brabus</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Minichamps</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Б/у</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Отправляю по всему миру - по возможности.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Mercedes C-Klasse 2011 W204 W 204 Schuco</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135744.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135654.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135703.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135716.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135721.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/img_20251123_135755.jpg</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7830441</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>9300</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Schuco</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Б/у</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкойПривезу любые модели на заказ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Audi RS4 RS 4 Avant  2018 Spark</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471219.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471242.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471236.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471229.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471223.jpg; https://scalebay.ru/uploads/user/f/o/fortythird_3839/1712674471213.jpg</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9331546</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9300</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>9600</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Audi</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Spark</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>В связи с колебаниями курса рубля, необходимо уточнять цену перед покупкой.Привезу любые модели на заказ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Skoda 706 RTTN с полуприцепом Alka N12CH   АИСТ</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-2.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-3.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-8.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-9.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-6.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-7.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-5.jpg; https://scalebay.ru/uploads/user/l/a/labtoz_20/skoda-706-rttn-s-polupricepom-alka-n12ch-114510-10.jpg</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7409184</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4100</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="n">
-        <v>4100</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Škoda</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Автоистория (АИСТ)</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>металл , пластик, резина</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Информация по оплате и отправке в разделе " Обо мне". Условия аукциона стандартные. выход на связь в течении 3 дней оплата в течении 7 дней с момента окончания аукциона. Все вопросы по лоту , оплате , отправке исключительно до покупки (до ставки) Смотрите мои другие лоты.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -63,10 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -530,6 +533,55 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>BERLIET 560K, grey</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/v/d/vdim_1858/1-8-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1518816</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Berliet</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -63,13 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -533,55 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>BERLIET 560K, grey</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/v/d/vdim_1858/1-8-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>1518816</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="n">
-        <v>1950</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Berliet</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Altaya</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -539,42 +539,44 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>BERLIET 560K, grey</t>
+          <t>Pickup w/ZPU-2, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/v/d/vdim_1858/1-8-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251023_153724-213x128.jpg</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1518816</t>
+          <t>3650138</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n">
+        <v>300</v>
+      </c>
       <c r="H2" s="2" t="n">
-        <v>1950</v>
+        <v>2090</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Berliet</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>Meng Model</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
@@ -582,6 +584,5687 @@
       <c r="N2" s="2" t="inlineStr"/>
       <c r="O2" s="2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>!!! УЦЕНКА Шасси УРАЛ-377 кабина хаки</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20241014_183426-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>4831510</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>УРАЛ</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Автоистория (АИСТ)</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Камаз-6520 рестайлинг самосвал.SSM.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/r/artmodel_31719/11-16-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>869462</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>8550</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1099-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1163031</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ЗИС 151</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-8-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>204531</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>ЗиС</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>ALF</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1129-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2767747</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1087-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2801311</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ-82 Беларусь</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0012-4-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3018733</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Traktoroexport</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1102-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3314893</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Datsun 240Z</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0053-6-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3346604</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>10800</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>11100</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Datsun</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Lancia Stratos Safari Type</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0061-4-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3714404</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8550</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Lancia</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Kingstar</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Thornycroft Van C846</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0132-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>375149</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Porsche 928</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0069-5-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3796480</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8550</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Kingstar</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1069-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>418619</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1126-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>433137</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Ford GT 70</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-2-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4945563</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1117-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5200545</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1081-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>582282</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen 1200 Police Car</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0027-10-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6012279</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>13300</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ 200</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0024-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>6104176</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Vektor-Models</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Rolls Royce Silver Shadow</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-23-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>6164799</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>8300</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Rolls-Royce</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Porsche Tagra 911 S</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0010-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6432719</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>12900</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>MGC G.T. Competition Model</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0002-26-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6590012</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Ford Mustang Mach 1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0043-9-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6905443</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8100</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>8400</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1084-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6926370</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1114-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>7031978</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Ford Cortina GXL</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>7337941</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>20700</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Bedford Type OB Coach C949/11</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0062-5-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>7440405</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>3900</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Bedford</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Renault 16 TS</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0046-8-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7507693</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>13500</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>13800</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Morris Marina 1.8 Coupe</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0019-12-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>762346</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Morris</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Mini Cooper S</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0038-12-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>783744</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Mini Cooper</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Lamborghini Silhouette S</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0018-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>7924589</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>8550</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Lamborghini</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Kingstar</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Rover 200 TC</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0002-3-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>80733</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>13500</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>13800</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1042-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>8327021</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1096-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>8453838</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1090-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>8799524</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1063-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>898982</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ЗИЛ 157</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0044-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>9075559</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>ALF</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1054-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>9216668</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1078-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>9307365</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen 1200 Saloon</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0089-3-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>9404771</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>10800</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>11100</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>824 1926 Renault Van</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0056-6-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>9871524</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Renault Galion 1959 Perrier IXO - Altaya</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_113323_edit_8072372465955-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>1011362</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Jelcz 315 1975 Atlas</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260501_142955_edit_232713947621259-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>3777694</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Jelcz</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Roman 10.FFP.1 1974 Atlas</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260501_142454_edit_232680322587931-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>4165329</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso 2011/50 Cabezón 1966 Auto Replicas - BKL (FR) 1/50</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/pegaso-2011-cabezon-1966-auto-replicas-bkl-fr-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>4251493</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Auto Réplicas - BKL (FR)</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ-5335 бортовой 1977 Легендарные грузовики СССР</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_113252_edit_8054217882104-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>5331825</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>MODIMIO</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Renault Rodéo 4 1971 Universal Hobbies для M6</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/mr4-04-renault-rodeo-4-1971-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>5672705</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Universal Hobbies (Renault 4)</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Morris J2 Van 1956 Post Office Telephones Vanguards с сертификатом</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/va10601-morris-j2-van-1956-post-office-telephones-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>610600</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Morris</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Vanguards</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Fiat 1100 E Furgone Servizio Prevenzione Vigili del fuoco Appiano Gentile 1949 Brumm</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/r178-fiat-1100-e-furgone-servizio-prevenzione-1949-brumm-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>638122</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Fiat</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Brumm</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot 504 - Lagos 1977 IXO - Altaya</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/5d5adf6e817af71fa336dceea2b639be-680x503-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>8821898</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Willeme LC 610 1953 Nez De Requin IXO / Altaya</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/cam-13-willeme-lc610-1953-nez-de-requin-ridelles-hautes-baches-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>9761992</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Willeme</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Altaya (Camions d’autrefois)</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Porsche 911 Dakar 2023</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150958.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150925.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150950.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151006.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151020.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151014.jpg</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>1391757</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>9198</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>9498</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Audi RS e-tron GT 2021 anthrazit</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195304.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939r.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195337.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195318.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195327.jpg</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>5884616</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>9298</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>9598</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen Hebmüller Cabriolet 1950</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102927-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102845-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102850-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102910-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102919-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102923-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102931-(1).jpg</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>7850859</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>4698</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>BMW E1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093319-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>1182046</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Citroen CX IXO</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182434-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>1185664</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Citroën</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>IXO Road (серии MOC, CLC)</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Renault Laguna III 2007 Norev</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182214-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>133380</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>BMW 335- 1939</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194658-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>1578519</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>BMW Z8 Cararama</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260525_181534-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>1601802</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Toyota Aristo 3.0V 1991 Hi-Story</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240808_101104-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>1694830</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>4700</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Hi-Story</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Toyota CELSIOR F Package 2004</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250728_133553-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>2024831</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Wit’s</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>BMW Dixi 3/15</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_184302-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>236328</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Schuco</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>BMW 750iL 1997 Tomorrow never dies</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_222923-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>2728564</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Eaglemoss</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>BMW 325i cabrio (E36) Cararama</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260525_182652-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>3003754</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>BMW 2000 (1966)</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_224842-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>3077575</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Schuco</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>BMW 5 (E60) 545i SEDAN 2003</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194153-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>3121919</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Kyosho</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Opel Senator A2 1982-1986</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240713_235102-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>3177662</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Opel Collection</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Honda Accord 9 cn-spec CR7 2013</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_172227-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>3213992</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Honda</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>BMW 325 turing wagon</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093005-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>3237056</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Lexus LS 460 2007</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_141330-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>3396867</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Lexus</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Provence Moulage</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Bentley MK VI 1950</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_173155-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>3431649</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Bentley</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>IXO Museum (серия MUS)</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Maserati Quattroporte V 2003</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240722_165116-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>37371</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Maserati</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>LEO models</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Alfa Romeo Giulietta police</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162722-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>400307</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Alfa Romeo</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Полицейские машины мира, Deagostini</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>BMW R1100RT</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_174858-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>4168369</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Lexus Lf-Sh 39th Tokyo motor show 2005 Wit’s</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_143046-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>4366405</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>8300</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Lexus</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>Wit’s</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Opel Vectra 2004</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194024-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>4569647</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Schuco</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Lancia Aprilia</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240405_171457-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>4591472</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Lancia</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Renault Safrane RXT 2.2 DT Tour de France Collection</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_184611-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>4865697</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot 404 1966 UH</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_001520-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>5416163</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Universal Hobbies</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>BMW M3</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240311_181332-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>5781398</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>AutoMax</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 cabrio M3 1988</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094004-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>5807662</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>BMW F650GS</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250714_143956-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>5818451</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Renault 21 2.0L Turbo phase 1 GTS 18.1 - 1988</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240807_132211-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>5870161</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Le Mans Miniatures</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>BMW 745i (E65)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194432-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>5897759</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz G63 AMG 2021 G-class</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260119_110944-4-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>6258793</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>7300</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>Almost real</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>BMW Z8</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_092818-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>6408410</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>BMW B-R25/3</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250714_143909-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>6912326</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Porsche 911 carrera cabrio</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250712_132722-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>7096026</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>MotorMax</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 cabrio M3 1995</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093830-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>7180354</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso Z102</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162455-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>7185152</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Jaguar XJ220 1992</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_174505-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>7294610</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Jaguar</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>DetailCars</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Opel Kapitan 1954</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_000850-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>7348819</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>2750</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>Starline</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>BMW 750Li F01 2009</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_092633-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>7517281</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Rastar</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>BMW 330i (E90)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094729-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>7706194</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Welly</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>BMW Z3 Z4 set</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240326_195906-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>7723072</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Opel Speedster</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162819-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>7862060</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Renault Safrane RXE V6 1993</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182024-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>7970594</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Богдан автобус школьный C-092S Vector</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250711_231912-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>7992629</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>16300</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Богдан</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Vector-Models</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Opel Rekord PI 4-doors 1957-1960</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240713_234631-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>8616703</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Opel Collection</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>BMW M5 E90</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_091800-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>8676363</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Rastar</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 (E90)</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094408-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>8688735</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Toyota Crown Royal Saloon G 2000</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_181612-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>8713237</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>J-Collection</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>BMW M5 E90</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_091848-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>8730895</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>BMW E46 3-series cabrio</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_151216-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>9254230</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>BMW CS Concept</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_202711-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>930889</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>9800</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>TRL models</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 coupe 2007</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093644-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>9423493</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Opel Kapitan P-LV 1959-63</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_181504-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>956046</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Opel Kapitan-Admiral-Diplomat 1969-77</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_180946-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>9656538</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Lotus seven</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162924-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>9828432</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Lotus</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>BMW 507</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093133-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>990891</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>ДЭ-210 (ЗиЛ-131)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/v/avtobusnik_6320/de-210-131-663854-2-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>9580455</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>5750</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>6050</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O113"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -539,17 +539,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pickup w/ZPU-2, 1/35, Meng Model</t>
+          <t>Pickup w/ZPU-1, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251023_153724-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251022_154644-213x128.jpg</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>3650138</t>
+          <t>1884650</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>!!! УЦЕНКА Шасси УРАЛ-377 кабина хаки</t>
+          <t>Pickup w/ZU-23-2, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20241014_183426-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251022_154600-213x128.jpg</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4831510</t>
+          <t>2016519</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -613,21 +613,21 @@
         <v>300</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1450</v>
+        <v>2090</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>УРАЛ</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Автоистория (АИСТ)</t>
+          <t>Meng Model</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
@@ -641,44 +641,44 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Камаз-6520 рестайлинг самосвал.SSM.</t>
+          <t>Pickup w/equipment, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/r/artmodel_31719/11-16-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251022_154620-213x128.jpg</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>869462</t>
+          <t>318750</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>8550</v>
+        <v>2090</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Start Scale Models (SSM)</t>
+          <t>Meng Model</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
@@ -692,17 +692,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Ford BB-157 Oil Tanker 1934 Ford Benzol Tins Toys</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1099-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_111314_edit_6704268775018-213x128.jpg</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1163031</t>
+          <t>1151990</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -719,17 +719,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Ford</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Tins Toys</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -743,22 +743,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ЗИС 151</t>
+          <t>Ferrari Dino 246 GTS Fabbri</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-8-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/fc-07-ferrari-dino-246-gts-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>204531</t>
+          <t>2008449</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -766,16 +766,16 @@
         <v>300</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>4800</v>
+        <v>1200</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>ЗиС</t>
+          <t>Ferrari</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>ALF</t>
+          <t>Ferrari Collection (Ge Fabbri)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Tatra (IGRA HO)</t>
+          <t>Rocar TV 12F Мașini de legendă DeAgostini</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1129-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/ml-17-rocar-tv-12f-masini-de-legenda-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2767747</t>
+          <t>2110424</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
@@ -817,21 +817,21 @@
         <v>300</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>Rocar</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Мașini de legendă DeAgostini</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
@@ -845,22 +845,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Chevrolet Corevette C2 Stingray 1963 DeAgostini</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1087-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/sc-77-chevrolet-corevette-c2-stingray-1963-213x128.jpg</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2801311</t>
+          <t>2333682</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -868,21 +868,21 @@
         <v>300</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>2300</v>
+        <v>1250</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Chevrolet</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Суперкары (без журнала)</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -896,22 +896,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>МТЗ-82 Беларусь</t>
+          <t>Ferrari 340 MM Fabbri</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0012-4-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/fc-36-ferrari-340-mm-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3018733</t>
+          <t>2448214</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -919,16 +919,16 @@
         <v>300</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1800</v>
+        <v>1050</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>МТЗ</t>
+          <t>Ferrari</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Traktoroexport</t>
+          <t>Ferrari Collection (Ge Fabbri)</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Fiat 500 C Belvedere 1949 Brumm</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1102-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/r049-fiat-500c-belvedere-1949-213x128.jpg</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3314893</t>
+          <t>4147654</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Fiat</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Brumm</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -998,22 +998,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Datsun 240Z</t>
+          <t>Trabant P50 Limousine 1959 DeAgostini</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0053-6-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/kap-86-trabant-p50-limousine-1959-213x128.jpg</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3346604</t>
+          <t>4276273</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1021,16 +1021,16 @@
         <v>300</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>11100</v>
+        <v>1500</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Datsun</t>
+          <t>Trabant</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>DeAgostini-Польша (Kultowe Auta)</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1049,22 +1049,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Lancia Stratos Safari Type</t>
+          <t>Fiat 500 C Furgoncino 1949 Ramazotti Brumm</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0061-4-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/r053-fiat-500c-furgoncinob-1949-ramazotti-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3714404</t>
+          <t>429518</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
@@ -1072,16 +1072,16 @@
         <v>300</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>8850</v>
+        <v>2800</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Lancia</t>
+          <t>Fiat</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Kingstar</t>
+          <t>Brumm</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Thornycroft Van C846</t>
+          <t>Panoz Esperante GTR-1 1998 IXO Models</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0132-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/cixj000036-panoz-esperante-gtr-1-1998-ixo-1-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>375149</t>
+          <t>4696181</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
@@ -1123,12 +1123,16 @@
         <v>300</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>4300</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+        <v>3100</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Panoz</t>
+        </is>
+      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>IXO Junior</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1147,22 +1151,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Porsche 928</t>
+          <t>Chevrolet 3100 1953 Road Champs</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0069-5-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/64825-chevrolet-3100-1953-road-champs-213x128.jpg</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3796480</t>
+          <t>5170923</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
@@ -1170,16 +1174,16 @@
         <v>300</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>8850</v>
+        <v>2800</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Chevrolet</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Kingstar</t>
+          <t>Road Champs</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1198,22 +1202,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Tatra (IGRA HO)</t>
+          <t>Chevrolet Corvette C3 Stingray 1978 DeAgostini</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1069-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/sc-63-chevrolet-corvette-c3-stingray-1978-213x128.jpg</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>418619</t>
+          <t>6567288</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>950</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
@@ -1221,21 +1225,21 @@
         <v>300</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>2800</v>
+        <v>1250</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>Chevrolet</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Суперкары (без журнала)</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr"/>
@@ -1249,22 +1253,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Tatra (IGRA HO)</t>
+          <t>Austin-Healey 3000 MkIII 1964 Schuco Junior Line</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1126-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/331-6337-austin-healey-3000-mkiii-1964-schuco-junior-line-213x128.jpg</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>433137</t>
+          <t>6991396</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1272,21 +1276,21 @@
         <v>300</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>2800</v>
+        <v>1500</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>Austin-Healey</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Grani &amp; Partners</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr"/>
@@ -1300,22 +1304,22 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Ford GT 70</t>
+          <t>Citroën HY Fourgon 1958 Colorgraf IXO - Vadis</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-2-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/vpe-21-citroen-hy-fourgon-1958-colorgraf-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4945563</t>
+          <t>785275</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
@@ -1323,16 +1327,16 @@
         <v>300</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>5300</v>
+        <v>2550</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Citroën</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>Vadis</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1351,22 +1355,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Tatra (IGRA HO)</t>
+          <t>Trabant P50 Kombi DeAgostini</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1117-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/kap-08-trabant-p50-kombi-kultowe_auta-prl-u-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5200545</t>
+          <t>8170173</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
@@ -1374,21 +1378,21 @@
         <v>300</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>2300</v>
+        <v>1050</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>Trabant</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>DeAgostini-Польша (Kultowe Auta)</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr"/>
@@ -1402,22 +1406,22 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Tatra (IGRA HO)</t>
+          <t>Honda 1300 Coupe 9 1970</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1081-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108265-213x128.jpg</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>582282</t>
+          <t>1286421</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
@@ -1425,21 +1429,21 @@
         <v>300</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>2800</v>
+        <v>3498</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr"/>
@@ -1453,22 +1457,22 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen 1200 Police Car</t>
+          <t>Porsche 911 Dakar 2023</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0027-10-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150958.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150925.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150950.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151006.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151020.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151014.jpg</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6012279</t>
+          <t>1391757</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
@@ -1476,16 +1480,16 @@
         <v>300</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>13300</v>
+        <v>9498</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
+          <t>Porsche</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>Minichamps</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1495,8 +1499,16 @@
       </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
-      <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1504,22 +1516,22 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>МАЗ 200</t>
+          <t>Toyota Windom 1991</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0024-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108252-213x128.jpg</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6104176</t>
+          <t>145548</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1527,16 +1539,16 @@
         <v>300</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>4300</v>
+        <v>3698</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Vektor-Models</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1555,22 +1567,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Rolls Royce Silver Shadow</t>
+          <t>Mitsubishi Jeep J30 1961</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-23-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108245-213x128.jpg</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6164799</t>
+          <t>2224108</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
@@ -1578,16 +1590,16 @@
         <v>300</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>8300</v>
+        <v>3498</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Rolls-Royce</t>
+          <t>Mitsubishi</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1606,22 +1618,22 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Porsche Tagra 911 S</t>
+          <t>Honda T360 Truck 1963</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0010-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108263-213x128.jpg</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6432719</t>
+          <t>2472935</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
@@ -1629,16 +1641,16 @@
         <v>300</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>12900</v>
+        <v>3498</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1657,22 +1669,22 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MGC G.T. Competition Model</t>
+          <t>Nissan Patrol 300 H-60 1970</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0002-26-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108294-213x128.jpg</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6590012</t>
+          <t>3188229</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
@@ -1680,16 +1692,16 @@
         <v>300</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>10300</v>
+        <v>3498</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>Nissan</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1708,22 +1720,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Ford Mustang Mach 1</t>
+          <t>Red Bull RB19 GP Austin USA  Verstappen 2023</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0043-9-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/103303-213x128.jpg</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6905443</t>
+          <t>4179369</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
@@ -1731,16 +1743,16 @@
         <v>300</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>8400</v>
+        <v>2298</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>Burago Signature</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1759,22 +1771,22 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Mercedes X-Class 2017</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1084-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/mercedes-x-klasse-norev-183421-6.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202209.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202532.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202414.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202238.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202319.jpg</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>6926370</t>
+          <t>4439325</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
@@ -1782,27 +1794,35 @@
         <v>300</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>2300</v>
+        <v>9598</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Norev</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:18</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
-      <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1810,22 +1830,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Tatra (IGRA HO)</t>
+          <t>Suzuki Carry Van 1969</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1114-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108293-213x128.jpg</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>7031978</t>
+          <t>4916751</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
@@ -1833,21 +1853,21 @@
         <v>300</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>2300</v>
+        <v>3498</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>Suzuki</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr"/>
@@ -1861,22 +1881,22 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Ford Cortina GXL</t>
+          <t>Audi RS e-tron GT 2021 anthrazit</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195304.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939r.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195337.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195318.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195327.jpg</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7337941</t>
+          <t>5884616</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
@@ -1884,27 +1904,35 @@
         <v>300</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>21000</v>
+        <v>9598</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Ford</t>
+          <t>Audi</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>Norev</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:18</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
-      <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -1912,22 +1940,22 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Bedford Type OB Coach C949/11</t>
+          <t>Honda S800 Cabrio 1966</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0062-5-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108270-213x128.jpg</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7440405</t>
+          <t>619178</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
@@ -1935,21 +1963,21 @@
         <v>300</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>3900</v>
+        <v>3498</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1:50</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr"/>
@@ -1963,22 +1991,22 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Renault 16 TS</t>
+          <t>Volkswagen Hebmüller Cabriolet 1950</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0046-8-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102927-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102845-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102850-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102910-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102919-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102923-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102931-(1).jpg</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7507693</t>
+          <t>7850859</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
@@ -1986,16 +2014,16 @@
         <v>300</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>13800</v>
+        <v>4698</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Renault</t>
+          <t>Volkswagen</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>Minichamps</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2005,8 +2033,16 @@
       </c>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -2014,22 +2050,22 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Morris Marina 1.8 Coupe</t>
+          <t>Toyota Sera 1990</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0019-12-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/108255-213x128.jpg</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>762346</t>
+          <t>8429217</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
@@ -2037,16 +2073,16 @@
         <v>300</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>10300</v>
+        <v>3498</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Morris</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>First 43 Models</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -2065,22 +2101,22 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Mini Cooper S</t>
+          <t>Тракторы: история, люди, машины №1 - МТЗ-50</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0038-12-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/20260408_172105-213x128.jpg</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>783744</t>
+          <t>8918879</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>498</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
@@ -2088,16 +2124,16 @@
         <v>300</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>6600</v>
+        <v>798</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Mini Cooper</t>
+          <t>МТЗ</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>Автолегенды СССР журнал от DeAgostini</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2116,22 +2152,22 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Lamborghini Silhouette S</t>
+          <t>Суперкары №24 Lexus LFA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0018-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/20260408_172126-213x128.jpg</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>7924589</t>
+          <t>9561195</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>350</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
@@ -2139,16 +2175,16 @@
         <v>300</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>8850</v>
+        <v>650</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Lamborghini</t>
+          <t>Lexus</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Kingstar</t>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2167,22 +2203,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Rover 200 TC</t>
+          <t>Масштабная модель Mercedes-Benz F500 Spark/Minimax B6 604 0428</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0002-3-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_154449-213x128.jpg</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>1089425</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
@@ -2190,16 +2226,16 @@
         <v>300</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>13800</v>
+        <v>7300</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Rover</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2218,22 +2254,22 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Масштабная модель Mercedes-Benz F300 Spark/Minimax B6 604 0426</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1042-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_155835-213x128.jpg</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>8327021</t>
+          <t>1256519</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
@@ -2241,21 +2277,21 @@
         <v>300</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>2800</v>
+        <v>7300</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr"/>
@@ -2269,22 +2305,22 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Масштабная модель Mercedes-Benz F200 Spark/Minimax B6 604 0425</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1096-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_154816-213x128.jpg</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8453838</t>
+          <t>1412463</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
@@ -2292,21 +2328,21 @@
         <v>300</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>2300</v>
+        <v>7300</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr"/>
@@ -2320,22 +2356,22 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Сборная модель Средний артиллерийский тягач АТС-59Г 3027AVD</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1090-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_506825_1768818697-213x128.jpg</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8799524</t>
+          <t>149089</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
@@ -2343,21 +2379,21 @@
         <v>300</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>2300</v>
+        <v>2900</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>АТС-59</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr"/>
@@ -2371,22 +2407,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Решетка радиатора для сборной модели ЗиЛ-130 бортовой 3501AVD</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1063-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20240708_101027_356476262183-213x128.jpg</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>898982</t>
+          <t>1583951</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
@@ -2394,21 +2430,21 @@
         <v>300</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>2800</v>
+        <v>400</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr"/>
@@ -2422,22 +2458,22 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ЗИЛ 157</t>
+          <t>Сборная модель Внутризаводской транспорт ПАЗ-3205 ВЗТ 0-11 1546AVD</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0044-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1546-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>9075559</t>
+          <t>1673857</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
@@ -2445,16 +2481,16 @@
         <v>300</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>4300</v>
+        <v>3300</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>ЗИЛ</t>
+          <t>ПАЗ</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>ALF</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2473,22 +2509,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+          <t>Сборная модель СУЛА-3990 1531AVD</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1054-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1531-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>9216668</t>
+          <t>2052076</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
@@ -2496,21 +2532,21 @@
         <v>300</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>2800</v>
+        <v>2300</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>ЛиАЗ</t>
+          <t>Сула</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr"/>
@@ -2524,22 +2560,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Tatra (IGRA HO)</t>
+          <t>Масштабная модель Троллейбус ЗиУ-5 белый 04006</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1078-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260314_181012-213x128.jpg</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>9307365</t>
+          <t>2135903</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
@@ -2547,21 +2583,21 @@
         <v>300</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>2800</v>
+        <v>5800</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Tatra</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Igra HO</t>
+          <t>Demprice</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>1:87</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr"/>
@@ -2575,22 +2611,22 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen 1200 Saloon</t>
+          <t>Масштабная модель Икарус 211 автобус 0289MP</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0089-3-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_519930_1778834484-213x128.jpg</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>9404771</t>
+          <t>2369353</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
@@ -2598,16 +2634,16 @@
         <v>300</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>11100</v>
+        <v>8250</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>ModelPro</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2626,22 +2662,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>824 1926 Renault Van</t>
+          <t>Сборная модель Бортовой автомобиль SKODA 100.05 1666AVD</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0056-6-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_497239_1763040049-213x128.jpg</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>9871524</t>
+          <t>2600982</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
@@ -2649,16 +2685,16 @@
         <v>300</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>4300</v>
+        <v>2500</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Renault</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Corgi Toys</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2677,22 +2713,22 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Renault Galion 1959 Perrier IXO - Altaya</t>
+          <t>Сборная модель Tatra T-138 NT 6x6 тягач (Татра) 1590AVD</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_113323_edit_8072372465955-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1590avd-tatra-t-138-nt-6x6-tyagach-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>1011362</t>
+          <t>2819982</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
@@ -2700,16 +2736,16 @@
         <v>300</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>2800</v>
+        <v>1950</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Renault</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2728,22 +2764,22 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Jelcz 315 1975 Atlas</t>
+          <t>Сборная модель СУЛА-3980 1610AVD</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260501_142955_edit_232713947621259-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1610-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3777694</t>
+          <t>3238630</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
@@ -2751,16 +2787,16 @@
         <v>300</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>3300</v>
+        <v>2300</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Jelcz</t>
+          <t>Сула</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2779,22 +2815,22 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Roman 10.FFP.1 1974 Atlas</t>
+          <t>Сборная модель КАМАЗ 5510 опытный самосвал 1695AVD</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260501_142454_edit_232680322587931-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_475167_1755254106-213x128.jpg</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>4165329</t>
+          <t>3658831</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
@@ -2802,16 +2838,16 @@
         <v>300</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>4300</v>
+        <v>4150</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Atlas</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2830,22 +2866,22 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Pegaso 2011/50 Cabezón 1966 Auto Replicas - BKL (FR) 1/50</t>
+          <t>Сборная модель ЗИЛ-133ГЯ бортовой 3511AVD</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/pegaso-2011-cabezon-1966-auto-replicas-bkl-fr-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_521957_1780999981-213x128.jpg</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>4251493</t>
+          <t>3800042</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
@@ -2853,21 +2889,21 @@
         <v>300</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Pegaso</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Auto Réplicas - BKL (FR)</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>1:50</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr"/>
@@ -2881,22 +2917,22 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>МАЗ-5335 бортовой 1977 Легендарные грузовики СССР</t>
+          <t>Сборная модель Ассенизационная машина ЦН-15 (ЗИС-5) 1575AVD</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_113252_edit_8054217882104-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1575-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>5331825</t>
+          <t>4033316</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
@@ -2904,16 +2940,16 @@
         <v>300</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>1300</v>
+        <v>1750</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>МАЗ</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>MODIMIO</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2932,22 +2968,22 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Renault Rodéo 4 1971 Universal Hobbies для M6</t>
+          <t>Сборная модель Вездеход ЗИЛ-132 1533AVD</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/mr4-04-renault-rodeo-4-1971-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/imagemagicopt-29-8-213x128.jpg</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>5672705</t>
+          <t>403798</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
@@ -2955,16 +2991,16 @@
         <v>300</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>1250</v>
+        <v>3400</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Renault</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Universal Hobbies (Renault 4)</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2983,22 +3019,22 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Morris J2 Van 1956 Post Office Telephones Vanguards с сертификатом</t>
+          <t>Сборная модель ЗИС-5 ПАРМ (1933)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/va10601-morris-j2-van-1956-post-office-telephones-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20190614_083450-213x128.jpg</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>610600</t>
+          <t>4297344</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
@@ -3006,16 +3042,16 @@
         <v>300</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>4300</v>
+        <v>2100</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Morris</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Vanguards</t>
+          <t>Miniclassic</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -3034,22 +3070,22 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Fiat 1100 E Furgone Servizio Prevenzione Vigili del fuoco Appiano Gentile 1949 Brumm</t>
+          <t>Сборная модель Автобус ИКАРУС 620 кабриолет 4079AVD</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/r178-fiat-1100-e-furgone-servizio-prevenzione-1949-brumm-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/4079avd-avtobus-ikarus-620-kabriolet-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>638122</t>
+          <t>4576064</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
@@ -3057,16 +3093,16 @@
         <v>300</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>2800</v>
+        <v>3300</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Fiat</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Brumm</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -3085,22 +3121,22 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Peugeot 504 - Lagos 1977 IXO - Altaya</t>
+          <t>Сборная модель Бронетранспортер ГТ-МУ 3023AVD</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/5d5adf6e817af71fa336dceea2b639be-680x503-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_506806_1768818557-213x128.jpg</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>8821898</t>
+          <t>4681141</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
@@ -3108,16 +3144,16 @@
         <v>300</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>2600</v>
+        <v>2550</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>ГТ-МУ</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -3136,22 +3172,22 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Willeme LC 610 1953 Nez De Requin IXO / Altaya</t>
+          <t>Сборная модель Кунг АК-34 (151) 1668AVD</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/cam-13-willeme-lc610-1953-nez-de-requin-ridelles-hautes-baches-1-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_467438_1748584081-213x128.jpg</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>9761992</t>
+          <t>485568</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
@@ -3159,16 +3195,16 @@
         <v>300</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Willeme</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Altaya (Camions d’autrefois)</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -3187,22 +3223,22 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Porsche 911 Dakar 2023</t>
+          <t>Масштабная модель Aurus Аурус Сенат черный бронированный 412307</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150958.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150925.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150950.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151006.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151020.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151014.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260618_164110-213x128.jpg</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1391757</t>
+          <t>4882927</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>14500</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
@@ -3210,16 +3246,16 @@
         <v>300</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>9498</v>
+        <v>14800</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Аурус</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>МиниМир</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -3229,16 +3265,8 @@
       </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr"/>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
@@ -3246,22 +3274,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Audi RS e-tron GT 2021 anthrazit</t>
+          <t>Масштабная модель Ilario Chromes Talbot Lago T26 1948 Chro064</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195304.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939r.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195337.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195318.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195327.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20251028_171533-213x128.jpg</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>5884616</t>
+          <t>5207889</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
@@ -3269,35 +3297,27 @@
         <v>300</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>9598</v>
+        <v>32300</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Audi</t>
+          <t>Talbot</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Norev</t>
+          <t>Ilario</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>1:18</t>
+          <t>1:43</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr"/>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3305,22 +3325,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen Hebmüller Cabriolet 1950</t>
+          <t>Сборная модель Reliant Robin (Рено) 1603AVD</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102927-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102845-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102850-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102910-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102919-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102923-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102931-(1).jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_401118_1677548741-213x128.jpg</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>7850859</t>
+          <t>5248549</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>4398</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
@@ -3328,16 +3348,16 @@
         <v>300</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>4698</v>
+        <v>2300</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen</t>
+          <t>Renault</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3347,16 +3367,8 @@
       </c>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.</t>
-        </is>
-      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -3364,22 +3376,22 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>BMW E1</t>
+          <t>Сборная модель Гусеничный транспортер-тягач ГТ-Т 3024AVD</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093319-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_506815_1768818619-213x128.jpg</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>1182046</t>
+          <t>5330136</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
@@ -3387,16 +3399,16 @@
         <v>300</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>900</v>
+        <v>2900</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ГТ-Т</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3415,22 +3427,22 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Citroen CX IXO</t>
+          <t>Масштабная модель KAMAZ-65225 седельный тягач 104172</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182434-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_467585_1748585240-213x128.jpg</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>1185664</t>
+          <t>554356</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
@@ -3438,16 +3450,16 @@
         <v>300</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>2800</v>
+        <v>3150</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Citroën</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>IXO Road (серии MOC, CLC)</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3466,22 +3478,22 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Renault Laguna III 2007 Norev</t>
+          <t>Масштабная модель Ilario Chromes Bugatti T46 S 1929 Chro048</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182214-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20251028_180616-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>133380</t>
+          <t>5672778</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>32000</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
@@ -3489,16 +3501,16 @@
         <v>300</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>4800</v>
+        <v>32300</v>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Renault</t>
+          <t>Bugatti</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Norev</t>
+          <t>Ilario</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3517,22 +3529,22 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>BMW 335- 1939</t>
+          <t>Сборная модель Каток СД-803 8015AVD</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194658-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/8015avd-sd-803-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>1578519</t>
+          <t>5893383</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
@@ -3540,16 +3552,16 @@
         <v>300</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>3300</v>
+        <v>3400</v>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>СД-803</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Altaya</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3568,22 +3580,22 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>BMW Z8 Cararama</t>
+          <t>Сборная модель АКЗ-51 мебельный фургон 1716AVD</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260525_181534-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_485338_1758284551-213x128.jpg</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>1601802</t>
+          <t>6812754</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
@@ -3591,16 +3603,16 @@
         <v>300</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>1550</v>
+        <v>3750</v>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ГАЗ</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3619,22 +3631,22 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Toyota Aristo 3.0V 1991 Hi-Story</t>
+          <t>Сборная модель Автобус IIKARUS 212 (Икарус) 4102AVD</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240808_101104-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_474867_1754918808-213x128.jpg</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>1694830</t>
+          <t>6903290</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
@@ -3642,16 +3654,16 @@
         <v>300</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>4700</v>
+        <v>4300</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Hi-Story</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3670,22 +3682,22 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Toyota CELSIOR F Package 2004</t>
+          <t>Сборная модель ЗИС-5 бортовой с тентом (1933)</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250728_133553-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20190614_083745-213x128.jpg</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2024831</t>
+          <t>6922032</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
@@ -3693,16 +3705,16 @@
         <v>300</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>5300</v>
+        <v>1950</v>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Toyota</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Wit’s</t>
+          <t>Miniclassic</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3721,22 +3733,22 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BMW Dixi 3/15</t>
+          <t>Сборная модель ЗИЛ-130В1 с полуприцепом ОДАЗ-794 7075AVD</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_184302-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/imagemagicopt-31-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>236328</t>
+          <t>7076407</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
@@ -3744,16 +3756,16 @@
         <v>300</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Schuco</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3772,22 +3784,22 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>BMW 750iL 1997 Tomorrow never dies</t>
+          <t>Сборная модель Тatra T500HB (Татра) автобус 4059AVD</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_222923-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/4059avd-tatra-t500hb-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>2728564</t>
+          <t>7089779</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
@@ -3795,16 +3807,16 @@
         <v>300</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>5300</v>
+        <v>3800</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Eaglemoss</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3823,22 +3835,22 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>BMW 325i cabrio (E36) Cararama</t>
+          <t>Сборная модель Дрезина Зил-130 4074AVD</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260525_182652-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/4074avd-drezina-zil-130-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>3003754</t>
+          <t>7249858</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
@@ -3846,16 +3858,16 @@
         <v>300</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>1800</v>
+        <v>3400</v>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3874,22 +3886,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>BMW 2000 (1966)</t>
+          <t>Сборная модель Tatra 148 VNM бортовой (Татра) 1591AVD</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_224842-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1591avd-tatra-148-vnm-bortovoj-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>3077575</t>
+          <t>7267272</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
@@ -3897,16 +3909,16 @@
         <v>300</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>4800</v>
+        <v>2500</v>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Schuco</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3925,22 +3937,22 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>BMW 5 (E60) 545i SEDAN 2003</t>
+          <t>Сборная модель УАЗ-САРЗ-2925 медицинский 1563AVD</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194153-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1563-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>3121919</t>
+          <t>7574227</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
@@ -3948,16 +3960,16 @@
         <v>300</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>5800</v>
+        <v>2250</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>УАЗ</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Kyosho</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3976,22 +3988,22 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Opel Senator A2 1982-1986</t>
+          <t>Сборная модель ТА-9А грузовой автомобиль 1717AVD</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240713_235102-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_497322_1763101502-213x128.jpg</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>3177662</t>
+          <t>7578471</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
@@ -3999,16 +4011,16 @@
         <v>300</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>2400</v>
+        <v>3400</v>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Opel</t>
+          <t>Тарту</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Opel Collection</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -4027,22 +4039,22 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Honda Accord 9 cn-spec CR7 2013</t>
+          <t>Сборная модель КАМАЗ-6522 (рестайлинг) самосвал 1685AVD</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_172227-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_472851_1751885300-213x128.jpg</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>3213992</t>
+          <t>76613</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
@@ -4050,16 +4062,16 @@
         <v>300</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>5300</v>
+        <v>2900</v>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>china</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -4078,22 +4090,22 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>BMW 325 turing wagon</t>
+          <t>Сборная модель Экскаватор UDS-110 (T-148) (Татра) 1595AVD</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093005-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1595avd-ekskavator-uds-110-t-148-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>3237056</t>
+          <t>7870977</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
@@ -4101,16 +4113,16 @@
         <v>300</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>2300</v>
+        <v>4250</v>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -4129,22 +4141,22 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Lexus LS 460 2007</t>
+          <t>Сборная модель Skoda-14Tr (Шкода) троллейбус 4022AVD</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_141330-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/4022avd-skoda-14tr-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>3396867</t>
+          <t>8025096</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
@@ -4152,16 +4164,16 @@
         <v>300</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>5800</v>
+        <v>3800</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Lexus</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Provence Moulage</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -4180,22 +4192,22 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Bentley MK VI 1950</t>
+          <t>Сборная модель Седельный тягач КРАЗ-258Б1 с полуприцепом ТЗ-22 7084AVD</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_173155-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_472921_1751885983-213x128.jpg</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>3431649</t>
+          <t>8092285</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
@@ -4203,16 +4215,16 @@
         <v>300</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>4300</v>
+        <v>4150</v>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Bentley</t>
+          <t>КрАЗ</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>IXO Museum (серия MUS)</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -4231,22 +4243,22 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Maserati Quattroporte V 2003</t>
+          <t>Масштабная модель Троллейбус ЗиУ-5 04006</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240722_165116-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260213_152359-213x128.jpg</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>37371</t>
+          <t>8487059</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
@@ -4254,16 +4266,16 @@
         <v>300</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>2050</v>
+        <v>5800</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Maserati</t>
+          <t>ЗиУ</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>LEO models</t>
+          <t>Demprice</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -4282,22 +4294,22 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Alfa Romeo Giulietta police</t>
+          <t>Сборная модель АМУР-53131 бортовой 3510AVD</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162722-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_518600_1777367048-213x128.jpg</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>400307</t>
+          <t>8763689</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
@@ -4305,21 +4317,21 @@
         <v>300</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>800</v>
+        <v>3000</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Alfa Romeo</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Полицейские машины мира, Deagostini</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr"/>
@@ -4333,22 +4345,22 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>BMW R1100RT</t>
+          <t>Сборная модель TATRA 815 V26 бортовая с тентом (Татра) 1433AVD</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_174858-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1433avd-tatra-815-v26-01-213x128.jpg</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>4168369</t>
+          <t>8827362</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
@@ -4356,16 +4368,16 @@
         <v>300</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>1050</v>
+        <v>3150</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -4384,22 +4396,22 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Lexus Lf-Sh 39th Tokyo motor show 2005 Wit’s</t>
+          <t>Сборная модель SKODA-M706RO фургон 1518AVD</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_143046-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1518-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>4366405</t>
+          <t>883129</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
@@ -4407,16 +4419,16 @@
         <v>300</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>8300</v>
+        <v>3400</v>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Lexus</t>
+          <t>Škoda</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Wit’s</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -4435,22 +4447,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Opel Vectra 2004</t>
+          <t>Сборная модель Пожарная автолестница АЛМ-30 (157) 1669AVD</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194024-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_467450_1748584138-213x128.jpg</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>4569647</t>
+          <t>8831869</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
@@ -4458,16 +4470,16 @@
         <v>300</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>4800</v>
+        <v>3750</v>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Opel</t>
+          <t>ЗИЛ</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Schuco</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4486,22 +4498,22 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Lancia Aprilia</t>
+          <t>BUDIG FULDAMOBIL TYPE N2 SILVER</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240405_171457-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20211215_014123-213x128.jpg</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>4591472</t>
+          <t>9104563</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
@@ -4509,16 +4521,16 @@
         <v>300</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>1250</v>
+        <v>5300</v>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Lancia</t>
+          <t>FULDAMOBIL</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Norev</t>
+          <t>Best of Show</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4537,22 +4549,22 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Renault Safrane RXT 2.2 DT Tour de France Collection</t>
+          <t>Сборная модель Тяжелый артиллерийский тягач АТ-Т 3022AVD</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_184611-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_506795_1768818513-213x128.jpg</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>4865697</t>
+          <t>9334614</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
@@ -4560,16 +4572,16 @@
         <v>300</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>4800</v>
+        <v>2900</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Renault</t>
+          <t>АТ-Т</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4588,22 +4600,22 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Peugeot 404 1966 UH</t>
+          <t>Сборная модель Пожарный автонасос ПМЗ-1 (ЗИС-11) 1574AVD</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_001520-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1574-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>5416163</t>
+          <t>9701550</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
@@ -4611,16 +4623,16 @@
         <v>300</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>2600</v>
+        <v>1950</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>Peugeot</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Universal Hobbies</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4639,22 +4651,22 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>BMW M3</t>
+          <t>Сборная модель Автобус 672А 4086AVD</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240311_181332-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_421118_1713350448-213x128.jpg</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>5781398</t>
+          <t>974153</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
@@ -4662,16 +4674,16 @@
         <v>300</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>1500</v>
+        <v>3800</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ПАЗ</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>AutoMax</t>
+          <t>AVD Models</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4690,22 +4702,22 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>BMW 3 cabrio M3 1988</t>
+          <t>Масштабная модель Mercedes-Benz F600 Spark/Minimax B6 604 0429</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094004-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_155326-213x128.jpg</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>5807662</t>
+          <t>9850934</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
@@ -4713,16 +4725,16 @@
         <v>300</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>1800</v>
+        <v>7300</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Mercedes-Benz</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>New-Ray Toys</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4741,22 +4753,22 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>BMW F650GS</t>
+          <t>Автобус ЗиС-154 Классик бас</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250714_143956-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/v/avtobusnik_6320/img_20260615_165357_454-213x128.jpg</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>5818451</t>
+          <t>1556407</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
@@ -4764,23 +4776,19 @@
         <v>300</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>1050</v>
+        <v>4200</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+          <t>Classicbus</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
       <c r="M84" s="2" t="inlineStr"/>
       <c r="N84" s="2" t="inlineStr"/>
@@ -4792,22 +4800,22 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Renault 21 2.0L Turbo phase 1 GTS 18.1 - 1988</t>
+          <t>КамАЗ-6522 самосвал белый</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240807_132211-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-2.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-1.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-4.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-3.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-7.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-5.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-8.jpg</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>5870161</t>
+          <t>1613562</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
@@ -4815,16 +4823,16 @@
         <v>300</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>2800</v>
+        <v>4200</v>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>Renault</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Le Mans Miniatures</t>
+          <t>ПАО КАМАЗ</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4832,10 +4840,26 @@
           <t>1:43</t>
         </is>
       </c>
-      <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
-      <c r="N85" s="2" t="inlineStr"/>
-      <c r="O85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Металл/пластмасса</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>104165</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Модель новая в оригинальной упаковке.Самовывоз в Москве от метро Строгино.Почта России или СДЭК от 500 рублей.Выход на связь 1 день, оплата на карту Альфа банка 5 дней.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -4843,22 +4867,22 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>BMW 745i (E65)</t>
+          <t>Бокс 27 см Классик Бас</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194432-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/v/avtobusnik_6320/img_20260707_070613_062-213x128.jpg</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>5897759</t>
+          <t>8666329</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
@@ -4866,23 +4890,15 @@
         <v>300</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>2050</v>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
+        <v>2300</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
+          <t>Classicbus</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
       <c r="M86" s="2" t="inlineStr"/>
       <c r="N86" s="2" t="inlineStr"/>
@@ -4894,22 +4910,22 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz G63 AMG 2021 G-class</t>
+          <t>Автобус Икарус 255.70 красный</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260119_110944-4-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/s/o/sova_7701/img_20240821_160531_1-213x128.jpg</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>6258793</t>
+          <t>3785921</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>6900</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
@@ -4917,16 +4933,16 @@
         <v>300</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>7300</v>
+        <v>7200</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Almost real</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4945,22 +4961,22 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>BMW Z8</t>
+          <t>ЛиАЗ-5256 жёлтый циркон</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_092818-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/s/o/sova_7701/img_20230927_163939-213x128.jpg</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>6408410</t>
+          <t>4272025</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
@@ -4968,16 +4984,16 @@
         <v>300</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>New-Ray Toys</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4996,22 +5012,22 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>BMW B-R25/3</t>
+          <t>Автобус ЛАЗ-695Н красный</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250714_143909-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/s/o/sova_7701/img_20250108_111606_1-213x128.jpg</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>6912326</t>
+          <t>7544010</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
@@ -5019,16 +5035,16 @@
         <v>300</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>1050</v>
+        <v>5300</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>ЛАЗ</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Bauer/Cararama/Hongwell</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -5047,22 +5063,22 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Porsche 911 carrera cabrio</t>
+          <t>ЛиАЗ-5256 синий танзанит</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250712_132722-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/s/o/sova_7701/img_20230927_165502_1-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>7096026</t>
+          <t>8687550</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
@@ -5070,16 +5086,16 @@
         <v>300</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>1050</v>
+        <v>4000</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>MotorMax</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -5098,22 +5114,22 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>BMW 3 cabrio M3 1995</t>
+          <t>Автобус Икарус 256.54 Киноварь</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093830-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/s/o/sova_7701/img_20231118_191021_1-213x128.jpg</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>7180354</t>
+          <t>92437</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
@@ -5121,16 +5137,16 @@
         <v>300</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>1800</v>
+        <v>9300</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Ikarus</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>New-Ray Toys</t>
+          <t>DEMPRICE</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -5143,1128 +5159,6 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr"/>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Pegaso Z102</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162455-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>7185152</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H92" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>Pegaso</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Jaguar XJ220 1992</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_174505-1-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>7294610</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H93" s="2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>Jaguar</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>DetailCars</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
-      <c r="N93" s="2" t="inlineStr"/>
-      <c r="O93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Opel Kapitan 1954</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_000850-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>7348819</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>2450</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H94" s="2" t="n">
-        <v>2750</v>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Opel</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>Starline</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
-      <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>BMW 750Li F01 2009</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_092633-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>7517281</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H95" s="2" t="n">
-        <v>950</v>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Rastar</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
-      <c r="N95" s="2" t="inlineStr"/>
-      <c r="O95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>BMW 330i (E90)</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094729-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>7706194</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H96" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>Welly</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
-      <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>BMW Z3 Z4 set</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240326_195906-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>7723072</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H97" s="2" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>Bauer/Cararama/Hongwell</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
-      <c r="N97" s="2" t="inlineStr"/>
-      <c r="O97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Opel Speedster</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162819-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>7862060</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H98" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>Opel</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Renault Safrane RXE V6 1993</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182024-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>7970594</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H99" s="2" t="n">
-        <v>2800</v>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Renault</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>Vitesse</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Богдан автобус школьный C-092S Vector</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250711_231912-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>7992629</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>16000</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H100" s="2" t="n">
-        <v>16300</v>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>Богдан</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Vector-Models</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Opel Rekord PI 4-doors 1957-1960</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240713_234631-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>8616703</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H101" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>Opel</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>Opel Collection</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>BMW M5 E90</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_091800-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>8676363</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H102" s="2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Rastar</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
-      <c r="N102" s="2" t="inlineStr"/>
-      <c r="O102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>BMW 3 (E90)</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094408-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>8688735</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H103" s="2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>Bauer/Cararama/Hongwell</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
-      <c r="N103" s="2" t="inlineStr"/>
-      <c r="O103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Toyota Crown Royal Saloon G 2000</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_181612-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>8713237</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H104" s="2" t="n">
-        <v>4800</v>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>Toyota</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>J-Collection</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>BMW M5 E90</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_091848-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>8730895</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H105" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>New-Ray Toys</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
-      <c r="N105" s="2" t="inlineStr"/>
-      <c r="O105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>BMW E46 3-series cabrio</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_151216-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>9254230</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H106" s="2" t="n">
-        <v>5300</v>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Bauer/Cararama/Hongwell</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>BMW CS Concept</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_202711-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>930889</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>9500</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H107" s="2" t="n">
-        <v>9800</v>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>TRL models</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
-      <c r="N107" s="2" t="inlineStr"/>
-      <c r="O107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>107</v>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>BMW 3 coupe 2007</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093644-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>9423493</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H108" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>New-Ray Toys</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
-      <c r="N108" s="2" t="inlineStr"/>
-      <c r="O108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Opel Kapitan P-LV 1959-63</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_181504-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>956046</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H109" s="2" t="n">
-        <v>4800</v>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>Opel</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>Minichamps</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
-      <c r="N109" s="2" t="inlineStr"/>
-      <c r="O109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Opel Kapitan-Admiral-Diplomat 1969-77</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_180946-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>9656538</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H110" s="2" t="n">
-        <v>4800</v>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>Opel</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>Minichamps</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
-      <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Lotus seven</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162924-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>9828432</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H111" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>Lotus</t>
-        </is>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
-        </is>
-      </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr"/>
-      <c r="N111" s="2" t="inlineStr"/>
-      <c r="O111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>BMW 507</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093133-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>990891</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H112" s="2" t="n">
-        <v>900</v>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>BMW</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>New-Ray Toys</t>
-        </is>
-      </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
-      <c r="N112" s="2" t="inlineStr"/>
-      <c r="O112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>ДЭ-210 (ЗиЛ-131)</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/v/avtobusnik_6320/de-210-131-663854-2-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>9580455</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H113" s="2" t="n">
-        <v>6050</v>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>ЗИЛ</t>
-        </is>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>Start Scale Models (SSM)</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
-      <c r="N113" s="2" t="inlineStr"/>
-      <c r="O113" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -539,22 +539,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Porsche 911 Dakar 2023</t>
+          <t>Pickup w/ZPU-1, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150958.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150925.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150950.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151006.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151020.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151014.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251022_154644-213x128.jpg</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1391757</t>
+          <t>1884650</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
@@ -562,35 +562,27 @@
         <v>300</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>9498</v>
+        <v>2090</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Porsche</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Minichamps</t>
+          <t>Meng Model</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -598,22 +590,22 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mercedes X-Class 2017</t>
+          <t>Pickup w/ZU-23-2, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/mercedes-x-klasse-norev-183421-6.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202209.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202532.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202414.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202238.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202319.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251022_154600-213x128.jpg</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4439325</t>
+          <t>2016519</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
@@ -621,35 +613,27 @@
         <v>300</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>9598</v>
+        <v>2090</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Norev</t>
+          <t>Meng Model</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>1:18</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -657,22 +641,22 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Audi RS e-tron GT 2021 anthrazit</t>
+          <t>Pickup w/equipment, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195304.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939r.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195337.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195318.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195327.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251022_154620-213x128.jpg</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5884616</t>
+          <t>318750</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
@@ -680,35 +664,27 @@
         <v>300</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>9598</v>
+        <v>2090</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Audi</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Norev</t>
+          <t>Meng Model</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1:18</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -716,22 +692,22 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Масштабная модель Mercedes-Benz F500 Spark/Minimax B6 604 0428</t>
+          <t>Pickup w/ZPU-2, 1/35, Meng Model</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_154449-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20251023_153724-213x128.jpg</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1089425</t>
+          <t>3650138</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
@@ -739,21 +715,21 @@
         <v>300</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>7300</v>
+        <v>2090</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>Toyota</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Meng Model</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
@@ -767,22 +743,22 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Масштабная модель Mercedes-Benz F300 Spark/Minimax B6 604 0426</t>
+          <t>!!! УЦЕНКА Шасси УРАЛ-377 кабина хаки</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_155835-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alex_77_685/img_20241014_183426-1-213x128.jpg</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1256519</t>
+          <t>4831510</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>1150</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
@@ -790,16 +766,16 @@
         <v>300</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>7300</v>
+        <v>1450</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>УРАЛ</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Автоистория (АИСТ)</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -818,39 +794,39 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Масштабная модель Mercedes-Benz F200 Spark/Minimax B6 604 0425</t>
+          <t>Камаз-6520 рестайлинг самосвал.SSM.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_154816-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/r/artmodel_31719/11-16-213x128.jpg</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1412463</t>
+          <t>869462</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>7300</v>
+        <v>8550</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>КамАЗ</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Start Scale Models (SSM)</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -869,22 +845,22 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>BUDIG FULDAMOBIL TYPE N2 SILVER</t>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20211215_014123-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1099-213x128.jpg</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9104563</t>
+          <t>1163031</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -892,21 +868,21 @@
         <v>300</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>5300</v>
+        <v>2300</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>FULDAMOBIL</t>
+          <t>ЛиАЗ</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Best of Show</t>
+          <t>Igra HO</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1:43</t>
+          <t>1:87</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -920,22 +896,22 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Масштабная модель Mercedes-Benz F600 Spark/Minimax B6 604 0429</t>
+          <t>ЗИС 151</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20260523_155326-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-8-213x128.jpg</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9850934</t>
+          <t>204531</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
@@ -943,16 +919,16 @@
         <v>300</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>7300</v>
+        <v>4800</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Mercedes-Benz</t>
+          <t>ЗиС</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>ALF</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -971,22 +947,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Автобус ЗиС-154 Классик бас</t>
+          <t>Tatra (IGRA HO)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/v/avtobusnik_6320/img_20260615_165357_454-213x128.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1129-213x128.jpg</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1556407</t>
+          <t>2767747</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
@@ -994,19 +970,23 @@
         <v>300</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>4200</v>
+        <v>2300</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>ЗиС</t>
+          <t>Tatra</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Classicbus</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr"/>
@@ -1018,22 +998,22 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>КамАЗ-6522 самосвал белый</t>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-2.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-1.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-4.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-3.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-7.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-5.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-8.jpg</t>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1087-213x128.jpg</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1613562</t>
+          <t>2801311</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
@@ -1041,43 +1021,7354 @@
         <v>300</v>
       </c>
       <c r="H11" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ-82 Беларусь</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0012-4-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3018733</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Traktoroexport</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1102-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3314893</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Datsun 240Z</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0053-6-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3346604</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10800</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>11100</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Datsun</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Lancia Stratos Safari Type</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0061-4-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3714404</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>8550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Lancia</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Kingstar</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Thornycroft Van C846</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0132-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>375149</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Porsche 928</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0069-5-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3796480</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>8550</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Kingstar</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr"/>
+      <c r="O17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1069-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>418619</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr"/>
+      <c r="O18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1126-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>433137</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Ford GT 70</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-2-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4945563</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1117-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>5200545</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1081-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>582282</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen 1200 Police Car</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0027-10-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>6012279</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13000</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>13300</v>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ 200</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0024-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6104176</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Vektor-Models</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Rolls Royce Silver Shadow</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-23-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6164799</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>8300</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Rolls-Royce</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Porsche Tagra 911 S</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0010-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6432719</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>12600</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>12900</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>MGC G.T. Competition Model</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0002-26-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>6590012</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Ford Mustang Mach 1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0043-9-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6905443</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8100</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>8400</v>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1084-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6926370</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1114-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>7031978</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Ford Cortina GXL</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0001-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>7337941</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>20700</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>21000</v>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bedford Type OB Coach C949/11</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0062-5-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>7440405</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>3900</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Bedford</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Renault 16 TS</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0046-8-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>7507693</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>13500</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>13800</v>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Morris Marina 1.8 Coupe</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0019-12-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>762346</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>10300</v>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Morris</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Mini Cooper S</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0038-12-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>783744</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Mini Cooper</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Lamborghini Silhouette S</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0018-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>7924589</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>8550</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>8850</v>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Lamborghini</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Kingstar</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Rover 200 TC</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0002-3-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>80733</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>13500</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>13800</v>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Rover</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1042-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>8327021</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1096-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>8453838</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1090-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>8799524</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1063-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>898982</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>ЗИЛ 157</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0044-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>9075559</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>ALF</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ (LIAZ IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1054-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>9216668</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>ЛиАЗ</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Tatra (IGRA HO)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_1078-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>9307365</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Tatra</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Igra HO</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>1:87</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen 1200 Saloon</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0089-3-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>9404771</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>10800</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>11100</v>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Volkswagen</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>824 1926 Renault Van</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/l/alevgen_18241/dsc_0056-6-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>9871524</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Corgi Toys</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Renault Galion 1959 Perrier IXO - Altaya</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_113323_edit_8072372465955-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>1011362</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Ford BB-157 Oil Tanker 1934 Ford Benzol Tins Toys</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_111314_edit_6704268775018-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>1151990</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Ford</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Tins Toys</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Ferrari Dino 246 GTS Fabbri</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/fc-07-ferrari-dino-246-gts-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>2008449</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Ferrari Collection (Ge Fabbri)</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Rocar TV 12F Мașini de legendă DeAgostini</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/ml-17-rocar-tv-12f-masini-de-legenda-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>2110424</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Rocar</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Мașini de legendă DeAgostini</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Chevrolet Corevette C2 Stingray 1963 DeAgostini</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/sc-77-chevrolet-corevette-c2-stingray-1963-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>2333682</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Chevrolet</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары (без журнала)</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Ferrari 340 MM Fabbri</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/fc-36-ferrari-340-mm-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>2448214</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Ferrari Collection (Ge Fabbri)</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Jelcz 315 1975 Atlas</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260501_142955_edit_232713947621259-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>3777694</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Jelcz</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Fiat 500 C Belvedere 1949 Brumm</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/r049-fiat-500c-belvedere-1949-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>4147654</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Fiat</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Brumm</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Roman 10.FFP.1 1974 Atlas</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260501_142454_edit_232680322587931-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>4165329</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Roman</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Atlas</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso 2011/50 Cabezón 1966 Auto Replicas - BKL (FR) 1/50</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/pegaso-2011-cabezon-1966-auto-replicas-bkl-fr-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>4251493</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Auto Réplicas - BKL (FR)</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Trabant P50 Limousine 1959 DeAgostini</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/kap-86-trabant-p50-limousine-1959-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>4276273</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Trabant</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>DeAgostini-Польша (Kultowe Auta)</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Fiat 500 C Furgoncino 1949 Ramazotti Brumm</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/r053-fiat-500c-furgoncinob-1949-ramazotti-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>429518</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Fiat</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Brumm</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Panoz Esperante GTR-1 1998 IXO Models</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/cixj000036-panoz-esperante-gtr-1-1998-ixo-1-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>4696181</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>3100</v>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Panoz</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>IXO Junior</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Chevrolet 3100 1953 Road Champs</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/64825-chevrolet-3100-1953-road-champs-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>5170923</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Chevrolet</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Road Champs</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ-5335 бортовой 1977 Легендарные грузовики СССР</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/img_20260523_113252_edit_8054217882104-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>5331825</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>МАЗ</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>MODIMIO</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Renault Rodéo 4 1971 Universal Hobbies для M6</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/mr4-04-renault-rodeo-4-1971-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>5672705</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Universal Hobbies (Renault 4)</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Morris J2 Van 1956 Post Office Telephones Vanguards с сертификатом</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/va10601-morris-j2-van-1956-post-office-telephones-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>610600</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Morris</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Vanguards</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Fiat 1100 E Furgone Servizio Prevenzione Vigili del fuoco Appiano Gentile 1949 Brumm</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/r178-fiat-1100-e-furgone-servizio-prevenzione-1949-brumm-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>638122</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Fiat</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Brumm</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Chevrolet Corvette C3 Stingray 1978 DeAgostini</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/sc-63-chevrolet-corvette-c3-stingray-1978-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>6567288</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Chevrolet</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары (без журнала)</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Austin-Healey 3000 MkIII 1964 Schuco Junior Line</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/331-6337-austin-healey-3000-mkiii-1964-schuco-junior-line-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>6991396</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Austin-Healey</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Grani &amp; Partners</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Citroën HY Fourgon 1958 Colorgraf IXO - Vadis</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/vpe-21-citroen-hy-fourgon-1958-colorgraf-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>785275</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>2250</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>2550</v>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Citroën</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Vadis</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Trabant P50 Kombi DeAgostini</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/kap-08-trabant-p50-kombi-kultowe_auta-prl-u-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>8170173</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Trabant</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>DeAgostini-Польша (Kultowe Auta)</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot 504 - Lagos 1977 IXO - Altaya</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/5d5adf6e817af71fa336dceea2b639be-680x503-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>8821898</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Willeme LC 610 1953 Nez De Requin IXO / Altaya</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/b/o/box_6330/cam-13-willeme-lc610-1953-nez-de-requin-ridelles-hautes-baches-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>9761992</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Willeme</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Altaya (Camions d’autrefois)</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Porsche 911 Dakar 2023</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150958.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150925.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150950.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151006.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151020.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151014.jpg</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>1391757</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>9198</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>9498</v>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Mercedes X-Class 2017</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/mercedes-x-klasse-norev-183421-6.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202209.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202532.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202414.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202238.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202319.jpg</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>4439325</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>9298</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>9598</v>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Audi RS e-tron GT 2021 anthrazit</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195304.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939r.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195337.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195318.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195327.jpg</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>5884616</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>9298</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>9598</v>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>1:18</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>Новый</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Тракторы: история, люди, машины №1 - МТЗ-50</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/20260408_172105-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>8918879</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>498</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>798</v>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>МТЗ</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Автолегенды СССР журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары №24 Lexus LFA</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/m/a/mandiby_7644/20260408_172126-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>9561195</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>650</v>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Lexus</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr L 586 NZG</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_155721-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>1125819</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>17300</v>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr PR 776 бульдозер WSI</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_151010-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>1151941</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>25300</v>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>WSI</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr T 264 самосвал Conrad</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_165051-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>1291831</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>40300</v>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Conrad</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>4020AVD Специальный армейский автобус АС-38</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/4020-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>249361</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>АС-38</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr R 9400 NZG</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_153515-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>2960452</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель БТР-60 ПБ СССР</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20241221_231012-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>4107794</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>БТР</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>Арсенал</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr PR 754 NZG</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_144742-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>4281382</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>12300</v>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr R 9800 NZG</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_172802-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>4335434</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>75300</v>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Сборная модель Плавающий танк ПТ-76 3015AVD</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/3015-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>5452189</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>1650</v>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>ПТ-76</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr PR 764 NZG</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_145952-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>5764964</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>15300</v>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr R 9100 экскаватор Conrad</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_164242-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>5799020</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>32000</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>Conrad</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Сборная модель КАЗ-608В с п/п ОДАЗ-885 7079AVD</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/7079-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>5873304</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>КАЗ</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель IKARUS-30 (Икарус) 0246MP</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/0246mp-ikarus-30-01-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>614228</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>7100</v>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Ikarus</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>ModelPro</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Сборная модель AA-13-60 (Камаз-6560) Пожарная автоцистерна 1476AVD</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/1476-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>623137</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>М-63 Урал-2, Наши мотоциклы №10</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/nm10-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>7099795</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>УРАЛ</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Наши Мотоциклы (MODIMIO Collections)</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>1:24</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Сборная модель Бецема АЦ/АТЗ-16 (KAMAZ-65207-87) 1656AVD</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/catalog_gallery_452794_1744109462-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>7794961</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>3150</v>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>КамАЗ</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Сборная модель ЗИЛ 47874А 4085AVD</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/4085avd-zil-47874a-01-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>838789</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>ЕрАЗ-763 LST023</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/lst023-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>8548332</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>3750</v>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>ЕрАЗ</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>Lastochka</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>4019AVD Сборная модель Автобус повышенной проходимости АПП-66</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/4019-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>9255714</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>ГАЗ</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>AVD Models</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr TA 230 Conrad</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_145304-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>9613326</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>15300</v>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>Conrad</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>BERLIET 560K, grey</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/v/d/vdim_1858/1-8-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>1518816</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="n">
+        <v>1950</v>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Berliet</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>BMW E1</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093319-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>1182046</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Citroen CX IXO</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182434-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>1185664</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Citroën</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>IXO Road (серии MOC, CLC)</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Renault Laguna III 2007 Norev</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182214-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>133380</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>BMW 335- 1939</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194658-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>1578519</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>Altaya</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>BMW Z8 Cararama</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260525_181534-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>1601802</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1550</v>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Toyota Aristo 3.0V 1991 Hi-Story</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240808_101104-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>1694830</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>4700</v>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Hi-Story</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Toyota CELSIOR F Package 2004</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250728_133553-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>2024831</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Wit’s</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>BMW Dixi 3/15</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_184302-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>236328</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Schuco</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>BMW 750iL 1997 Tomorrow never dies</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_222923-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>2728564</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Eaglemoss</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr"/>
+      <c r="O105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>BMW 325i cabrio (E36) Cararama</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260525_182652-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>3003754</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr"/>
+      <c r="O106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>BMW 2000 (1966)</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_224842-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>3077575</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Schuco</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr"/>
+      <c r="O107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>BMW 5 (E60) 545i SEDAN 2003</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194153-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>3121919</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Kyosho</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr"/>
+      <c r="O108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Opel Senator A2 1982-1986</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240713_235102-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>3177662</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>2400</v>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Opel Collection</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr"/>
+      <c r="O109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Honda Accord 9 cn-spec CR7 2013</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_172227-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>3213992</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>Honda</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>china</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr"/>
+      <c r="O110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>BMW 325 turing wagon</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093005-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>3237056</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>2300</v>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr"/>
+      <c r="O111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Lexus LS 460 2007</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_141330-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>3396867</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>5800</v>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>Lexus</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Provence Moulage</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
+      <c r="N112" s="2" t="inlineStr"/>
+      <c r="O112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Bentley MK VI 1950</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_173155-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>3431649</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>4300</v>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>Bentley</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>IXO Museum (серия MUS)</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr"/>
+      <c r="O113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Maserati Quattroporte V 2003</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240722_165116-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>37371</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>Maserati</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>LEO models</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr"/>
+      <c r="O114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Alfa Romeo Giulietta police</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162722-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>400307</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>Alfa Romeo</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Полицейские машины мира, Deagostini</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr"/>
+      <c r="O115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>BMW R1100RT</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_174858-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>4168369</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
+      <c r="N116" s="2" t="inlineStr"/>
+      <c r="O116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Lexus Lf-Sh 39th Tokyo motor show 2005 Wit’s</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_143046-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>4366405</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>8300</v>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>Lexus</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Wit’s</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
+      <c r="N117" s="2" t="inlineStr"/>
+      <c r="O117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Opel Vectra 2004</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194024-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>4569647</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Schuco</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
+      <c r="N118" s="2" t="inlineStr"/>
+      <c r="O118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Lancia Aprilia</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240405_171457-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>4591472</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>1250</v>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Lancia</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Norev</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
+      <c r="N119" s="2" t="inlineStr"/>
+      <c r="O119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Renault Safrane RXT 2.2 DT Tour de France Collection</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_184611-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>4865697</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
+      <c r="N120" s="2" t="inlineStr"/>
+      <c r="O120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot 404 1966 UH</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_001520-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>5416163</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>Peugeot</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Universal Hobbies</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
+      <c r="N121" s="2" t="inlineStr"/>
+      <c r="O121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>BMW M3</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240311_181332-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>5781398</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>AutoMax</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
+      <c r="N122" s="2" t="inlineStr"/>
+      <c r="O122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 cabrio M3 1988</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094004-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>5807662</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
+      <c r="N123" s="2" t="inlineStr"/>
+      <c r="O123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>BMW F650GS</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250714_143956-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>5818451</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
+      <c r="N124" s="2" t="inlineStr"/>
+      <c r="O124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Renault 21 2.0L Turbo phase 1 GTS 18.1 - 1988</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240807_132211-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>5870161</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Le Mans Miniatures</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
+      <c r="N125" s="2" t="inlineStr"/>
+      <c r="O125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>BMW 745i (E65)</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_194432-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>5897759</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>2050</v>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
+      <c r="N126" s="2" t="inlineStr"/>
+      <c r="O126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz G63 AMG 2021 G-class</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260119_110944-4-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>6258793</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>7300</v>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Almost real</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr"/>
+      <c r="O127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>BMW Z8</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_092818-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>6408410</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr"/>
+      <c r="O128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>BMW B-R25/3</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250714_143909-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>6912326</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr"/>
+      <c r="O129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Porsche 911 carrera cabrio</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250712_132722-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>7096026</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Porsche</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>MotorMax</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr"/>
+      <c r="O130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 cabrio M3 1995</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093830-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>7180354</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr"/>
+      <c r="O131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso Z102</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162455-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>7185152</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Pegaso</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr"/>
+      <c r="O132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Jaguar XJ220 1992</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250715_174505-1-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>7294610</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>3200</v>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Jaguar</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>DetailCars</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr"/>
+      <c r="O133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Opel Kapitan 1954</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_000850-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>7348819</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>2750</v>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Starline</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr"/>
+      <c r="O134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>BMW 750Li F01 2009</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_092633-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>7517281</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Rastar</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr"/>
+      <c r="O135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>BMW 330i (E90)</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094729-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>7706194</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Welly</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr"/>
+      <c r="O136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>BMW Z3 Z4 set</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/20240326_195906-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>7723072</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr"/>
+      <c r="O137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Opel Speedster</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162819-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>7862060</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr"/>
+      <c r="O138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Renault Safrane RXE V6 1993</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_182024-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>7970594</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Renault</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Vitesse</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr"/>
+      <c r="O139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Богдан автобус школьный C-092S Vector</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250711_231912-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>7992629</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>16000</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>16300</v>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Богдан</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Vector-Models</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr"/>
+      <c r="O140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Opel Rekord PI 4-doors 1957-1960</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240713_234631-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>8616703</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Opel Collection</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr"/>
+      <c r="O141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>BMW M5 E90</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_091800-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>8676363</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Rastar</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr"/>
+      <c r="O142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 (E90)</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_094408-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>8688735</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>1300</v>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr"/>
+      <c r="O143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Toyota Crown Royal Saloon G 2000</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_181612-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>8713237</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>Toyota</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>J-Collection</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr"/>
+      <c r="O144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>BMW M5 E90</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_091848-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>8730895</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr"/>
+      <c r="O145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>BMW E46 3-series cabrio</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20250719_151216-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>9254230</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Bauer/Cararama/Hongwell</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr"/>
+      <c r="O146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>BMW CS Concept</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_202711-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>930889</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>9500</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>9800</v>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>TRL models</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr"/>
+      <c r="O147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>BMW 3 coupe 2007</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093644-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>9423493</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr"/>
+      <c r="O148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Opel Kapitan P-LV 1959-63</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_181504-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>956046</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr"/>
+      <c r="O149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Opel Kapitan-Admiral-Diplomat 1969-77</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260522_180946-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>9656538</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>4800</v>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Opel</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Minichamps</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr"/>
+      <c r="O150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Lotus seven</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20240714_162924-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>9828432</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>500</v>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Lotus</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Суперкары. Лучшие автомобили мира, журнал от DeAgostini</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr"/>
+      <c r="O151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>BMW 507</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/w/e/welga_29606/img_20260523_093133-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>990891</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>BMW</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>New-Ray Toys</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr"/>
+      <c r="O152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>КамАЗ-6522 самосвал белый</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-2.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-1.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-4.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-3.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-7.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-5.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-8.jpg</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>1613562</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H153" s="2" t="n">
         <v>4200</v>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>КамАЗ</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>ПАО КАМАЗ</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
         <is>
           <t>Металл/пластмасса</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M153" s="2" t="inlineStr">
         <is>
           <t>104165</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="N153" s="2" t="inlineStr">
         <is>
           <t>Новый</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="O153" s="2" t="inlineStr">
         <is>
           <t>Модель новая в оригинальной упаковке.Самовывоз в Москве от метро Строгино.Почта России или СДЭК от 500 рублей.Выход на связь 1 день, оплата на карту Альфа банка 5 дней.</t>
         </is>
       </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>ДЭ-210 (ЗиЛ-131)</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/a/v/avtobusnik_6320/de-210-131-663854-2-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>9580455</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>5750</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>6050</v>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>ЗИЛ</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Start Scale Models (SSM)</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr"/>
+      <c r="O154" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -63,13 +63,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -436,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -533,411 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Камаз-6520 рестайлинг самосвал.SSM.</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/r/artmodel_31719/11-16-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>869462</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>8500</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>8550</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>КамАЗ</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Start Scale Models (SSM)</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Porsche 911 Dakar 2023</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150958.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150925.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_150950.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151006.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151020.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20240517_151014.jpg</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>1391757</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>9198</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>9498</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Porsche</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Minichamps</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Mercedes X-Class 2017</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/mercedes-x-klasse-norev-183421-6.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202209.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202532.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202414.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202238.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20200121_202319.jpg</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4439325</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9298</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>9598</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Mercedes-Benz</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Norev</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1:18</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Audi RS e-tron GT 2021 anthrazit</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195304.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/89939r.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195227.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195337.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195318.jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20211008_195327.jpg</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5884616</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9298</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>9598</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Audi</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Norev</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1:18</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.При отправке почтой,гарантирую надежную упаковку.Возможно объединение нескольких лотов. Отвечу на все Ваши вопросы (до покупки)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Volkswagen Hebmüller Cabriolet 1950</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102927-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102845-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102850-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102910-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102919-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102923-(1).jpg; https://scalebay.ru/uploads/user/m/a/mandiby_7644/20250421_102931-(1).jpg</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7850859</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4398</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>4698</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Volkswagen</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Minichamps</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Модель абсолютно новая.доставалась из коробки только для фотографирования.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>КамАЗ-6522 самосвал белый</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-2.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-1.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-4.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-3.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-7.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-5.jpg; https://scalebay.ru/uploads/user/a/v/avtobusnik_6320/kamaz-6522-655359-8.jpg</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1613562</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3900</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>4200</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>КамАЗ</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>ПАО КАМАЗ</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>Металл/пластмасса</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>104165</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>Новый</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>Модель новая в оригинальной упаковке.Самовывоз в Москве от метро Строгино.Почта России или СДЭК от 500 рублей.Выход на связь 1 день, оплата на карту Альфа банка 5 дней.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>ДЭ-210 (ЗиЛ-131)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>https://scalebay.ru/uploads/cache/user/a/v/avtobusnik_6320/de-210-131-663854-2-213x128.jpg</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9580455</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5750</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>6050</v>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>ЗИЛ</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Start Scale Models (SSM)</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1:43</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -63,10 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -530,6 +533,516 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr L 586 NZG</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_155721-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1125819</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>17300</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
+      <c r="O2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr PR 776 бульдозер WSI</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_151010-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1151941</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>25000</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>25300</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>WSI</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr T 264 самосвал Conrad</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_165051-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1291831</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>40300</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Conrad</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr R 9400 NZG</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_153515-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2960452</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>45300</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель БТР-60 ПБ СССР</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20241221_231012-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4107794</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>3800</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>БТР</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Арсенал</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1:43</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr PR 754 NZG</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_144742-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4281382</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>12300</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr R 9800 NZG</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_172802-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4335434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>75300</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr PR 764 NZG</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_145952-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>5764964</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>15300</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>NZG</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr R 9100 экскаватор Conrad</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_164242-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5799020</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32000</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>32300</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Conrad</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Масштабная модель Liebherr TA 230 Conrad</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>https://scalebay.ru/uploads/cache/user/n/i/nik6001_303/img_20250211_145304-213x128.jpg</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9613326</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>15300</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Conrad</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1:50</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дальние" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Дальние" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/scalebay_latest_far.xlsx
+++ b/scalebay_latest_far.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Дальние" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дальние" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
